--- a/Бюджет Мясо и Рыба.xlsx
+++ b/Бюджет Мясо и Рыба.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Desktop\Новая папка\Заполнено_в работу\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70CF66FD-D911-4590-873D-8F4650D93D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D3D6C6-152A-4F11-8EAA-924183C82D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FF12FF6A-576F-45FA-986C-8AD372A54A11}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Средний чек</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>Призовой фонд</t>
+  </si>
+  <si>
+    <t>налоги на ФОТ ФУД (*1,46)</t>
+  </si>
+  <si>
+    <t>смена</t>
   </si>
 </sst>
 </file>
@@ -438,7 +444,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
@@ -508,6 +514,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Денежный" xfId="1" builtinId="4"/>
@@ -824,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0EBC7B-B4BB-4006-87AF-6138033E1037}">
-  <dimension ref="C1:I39"/>
+  <dimension ref="C1:I40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="54.6328125" customWidth="1"/>
@@ -869,129 +876,128 @@
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
+        <v>36</v>
+      </c>
+      <c r="D5" s="55">
+        <v>0.46</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G8" s="3" t="s">
+    <row r="9" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="3:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C9" s="5" t="s">
+    <row r="10" spans="3:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="7">
-        <f>G12-G19</f>
-        <v>1620787.2340425532</v>
-      </c>
-      <c r="H9" s="7">
-        <f>H12-H19</f>
-        <v>1676319.1489361702</v>
-      </c>
-      <c r="I9" s="8">
-        <f>SUM(G9:H9)</f>
-        <v>3297106.3829787234</v>
-      </c>
-    </row>
-    <row r="10" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="3:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="12" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7">
+        <f>G13-G20</f>
+        <v>825447.23404255323</v>
+      </c>
+      <c r="H10" s="7">
+        <f>H13-H20</f>
+        <v>880979.14893617015</v>
+      </c>
+      <c r="I10" s="8">
+        <f>SUM(G10:H10)</f>
+        <v>1706426.3829787234</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="3:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14">
-        <f>G12</f>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14">
+        <f>G13</f>
         <v>7500000</v>
       </c>
-      <c r="H11" s="14">
-        <f>H12+G11</f>
+      <c r="H12" s="14">
+        <f>H13+G12</f>
         <v>15000000</v>
       </c>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C12" s="15" t="s">
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16">
-        <f>SUM(G13:G17)</f>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16">
+        <f>SUM(G14:G18)</f>
         <v>7500000</v>
       </c>
-      <c r="H12" s="17">
-        <f>SUM(H13:H17)</f>
+      <c r="H13" s="17">
+        <f>SUM(H14:H18)</f>
         <v>7500000</v>
       </c>
-      <c r="I12" s="8">
-        <f>SUM(G12:H12)</f>
+      <c r="I13" s="8">
+        <f>SUM(G13:H13)</f>
         <v>15000000</v>
       </c>
     </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C13" s="18" t="s">
+    <row r="14" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C14" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="19">
-        <f>D2*D1</f>
-        <v>7500000</v>
-      </c>
-      <c r="H13" s="20">
-        <f>D1*D3</f>
-        <v>7500000</v>
-      </c>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20"/>
+      <c r="G14" s="19">
+        <f>D2*D1</f>
+        <v>7500000</v>
+      </c>
+      <c r="H14" s="20">
+        <f>D1*D3</f>
+        <v>7500000</v>
+      </c>
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.35">
@@ -1012,383 +1018,377 @@
       <c r="H16" s="20"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="23"/>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="3:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C18" s="24" t="s">
+    <row r="18" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="3:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="26">
-        <f>G19</f>
-        <v>5879212.7659574468</v>
-      </c>
-      <c r="H18" s="27">
-        <f>G18+H19</f>
-        <v>11702893.617021278</v>
-      </c>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C19" s="28" t="s">
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="26">
+        <f>G20</f>
+        <v>6674552.7659574468</v>
+      </c>
+      <c r="H19" s="27">
+        <f>G19+H20</f>
+        <v>13293573.617021278</v>
+      </c>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C20" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29">
-        <f>G20+G21+G22+G23+G24+G29++G35+G36+G37+G38</f>
-        <v>5879212.7659574468</v>
-      </c>
-      <c r="H19" s="30">
-        <f>H20+H21+H22+H23+H24+H29+H35+H36+H37+H38</f>
-        <v>5823680.8510638298</v>
-      </c>
-      <c r="I19" s="31">
-        <f>SUM(G19:H19)</f>
-        <v>11702893.617021278</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C20" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="34">
-        <v>400000</v>
-      </c>
-      <c r="H20" s="34">
-        <v>400000</v>
-      </c>
-      <c r="I20" s="35">
-        <f>G20+H20</f>
-        <v>800000</v>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29">
+        <f>G21+G22+G23+G24+G25+G30++G36+G37+G38+G39</f>
+        <v>6674552.7659574468</v>
+      </c>
+      <c r="H20" s="30">
+        <f>H21+H22+H23+H24+H25+H30+H36+H37+H38+H39</f>
+        <v>6619020.8510638298</v>
+      </c>
+      <c r="I20" s="31">
+        <f>SUM(G20:H20)</f>
+        <v>13293573.617021278</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C21" s="32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
       <c r="F21" s="33"/>
       <c r="G21" s="34">
+        <v>400000</v>
+      </c>
+      <c r="H21" s="34">
+        <v>400000</v>
+      </c>
+      <c r="I21" s="35">
+        <f>G21+H21</f>
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C22" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="34">
         <v>30000</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H22" s="36">
         <v>0</v>
       </c>
-      <c r="I21" s="35">
-        <f t="shared" ref="I21:I38" si="0">G21+H21</f>
+      <c r="I22" s="35">
+        <f t="shared" ref="I22:I39" si="0">G22+H22</f>
         <v>30000</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C22" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="37">
-        <f>D1*D2*D4</f>
-        <v>1725000</v>
-      </c>
-      <c r="H22" s="38">
-        <f>D1*D3*D4</f>
-        <v>1725000</v>
-      </c>
-      <c r="I22" s="35">
-        <f t="shared" si="0"/>
-        <v>3450000</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C23" s="18" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
-      <c r="G23" s="39">
-        <v>0</v>
-      </c>
-      <c r="H23" s="40">
-        <v>0</v>
+      <c r="G23" s="37">
+        <f>D1*D2*D4</f>
+        <v>1725000</v>
+      </c>
+      <c r="H23" s="38">
+        <f>D1*D3*D4</f>
+        <v>1725000</v>
       </c>
       <c r="I23" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3450000</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C24" s="41" t="s">
-        <v>19</v>
+      <c r="C24" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="39">
-        <f>SUM(G25:G28)</f>
-        <v>1729000</v>
-      </c>
-      <c r="H24" s="39">
-        <f>SUM(H25:H28)</f>
-        <v>1729000</v>
+        <v>0</v>
+      </c>
+      <c r="H24" s="40">
+        <v>0</v>
       </c>
       <c r="I24" s="35">
         <f t="shared" si="0"/>
-        <v>3458000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C25" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="42">
-        <v>12</v>
-      </c>
-      <c r="E25" s="43">
-        <v>6500</v>
-      </c>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43">
-        <f>E25*D25*D5</f>
-        <v>546000</v>
-      </c>
-      <c r="H25" s="20">
-        <f>E25*D25*D6</f>
-        <v>546000</v>
-      </c>
-      <c r="I25" s="44">
-        <f>G25+H25</f>
-        <v>1092000</v>
+      <c r="C25" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="39">
+        <f>SUM(G26:G29)</f>
+        <v>2524340</v>
+      </c>
+      <c r="H25" s="39">
+        <f>SUM(H26:H29)</f>
+        <v>2524340</v>
+      </c>
+      <c r="I25" s="35">
+        <f t="shared" si="0"/>
+        <v>5048680</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C26" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="42">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E26" s="43">
-        <v>4000</v>
-      </c>
-      <c r="F26" s="43"/>
+        <v>6500</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>37</v>
+      </c>
       <c r="G26" s="43">
-        <f>E26*D26*D5</f>
-        <v>168000</v>
+        <f>(E26*D26)*1.46*D6</f>
+        <v>797160</v>
       </c>
       <c r="H26" s="20">
-        <f>E26*D26*D6</f>
-        <v>168000</v>
+        <f>(E26*D26)*1.46*D7</f>
+        <v>797160</v>
       </c>
       <c r="I26" s="44">
-        <f t="shared" si="0"/>
-        <v>336000</v>
+        <f>G26+H26</f>
+        <v>1594320</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C27" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="42">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E27" s="43">
         <v>4000</v>
       </c>
-      <c r="F27" s="43"/>
+      <c r="F27" s="18" t="s">
+        <v>37</v>
+      </c>
       <c r="G27" s="43">
-        <f>E27*D27*D5</f>
-        <v>700000</v>
+        <f>(E27*D27)*1.46*D6</f>
+        <v>245280</v>
       </c>
       <c r="H27" s="20">
-        <f>E27*D27*D6</f>
-        <v>700000</v>
+        <f>(E27*D27)*1.46*D7</f>
+        <v>245280</v>
       </c>
       <c r="I27" s="44">
         <f t="shared" si="0"/>
-        <v>1400000</v>
+        <v>490560</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C28" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" s="42">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E28" s="43">
-        <v>4500</v>
-      </c>
-      <c r="F28" s="43"/>
+        <v>4000</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>37</v>
+      </c>
       <c r="G28" s="43">
-        <f>E28*D28*D6</f>
-        <v>315000</v>
+        <f>(E28*D28)*1.46*D6</f>
+        <v>1022000</v>
       </c>
       <c r="H28" s="20">
-        <f>E28*D28*D6</f>
-        <v>315000</v>
+        <f>(E28*D28)*1.46*D7</f>
+        <v>1022000</v>
       </c>
       <c r="I28" s="44">
         <f t="shared" si="0"/>
-        <v>630000</v>
+        <v>2044000</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="42">
+        <v>10</v>
+      </c>
+      <c r="E29" s="43">
+        <v>4500</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="43">
+        <f>(E29*D29)*1.46*D6</f>
+        <v>459900</v>
+      </c>
+      <c r="H29" s="20">
+        <f>(E29*D29)*1.46*D7</f>
+        <v>459900</v>
+      </c>
+      <c r="I29" s="44">
+        <f t="shared" si="0"/>
+        <v>919800</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C30" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46">
-        <f>SUM(G30:G34)</f>
+      <c r="D30" s="45"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46">
+        <f>SUM(G31:G35)</f>
         <v>670212.76595744689</v>
       </c>
-      <c r="H29" s="38">
-        <f>SUM(H30:H34)</f>
+      <c r="H30" s="38">
+        <f>SUM(H31:H35)</f>
         <v>644680.85106382985</v>
       </c>
-      <c r="I29" s="35">
+      <c r="I30" s="35">
         <f t="shared" si="0"/>
         <v>1314893.6170212766</v>
       </c>
     </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C30" s="18" t="s">
+    <row r="31" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C31" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D31" s="42">
         <v>1</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E31" s="43">
         <v>4000</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F31" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="43">
-        <f>(E30*D30*5*D5)/0.94</f>
+      <c r="G31" s="43">
+        <f>(E31*D31*5*D6)/0.94</f>
         <v>148936.17021276595</v>
       </c>
-      <c r="H30" s="43">
-        <f>(D30*E30*5*D6)/0.94</f>
+      <c r="H31" s="43">
+        <f>(D31*E31*5*D7)/0.94</f>
         <v>148936.17021276595</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I31" s="44">
         <f t="shared" si="0"/>
         <v>297872.3404255319</v>
       </c>
     </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C31" s="18" t="s">
+    <row r="32" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C32" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="47">
+      <c r="D32" s="47">
         <v>4</v>
       </c>
-      <c r="E31" s="43">
+      <c r="E32" s="43">
         <v>2000</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F32" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="43">
-        <f>(E31*D31*5*D5)/0.94</f>
+      <c r="G32" s="43">
+        <f>(E32*D32*5*D6)/0.94</f>
         <v>297872.3404255319</v>
       </c>
-      <c r="H31" s="48">
-        <f>(E31*D31*5*D6)/0.94</f>
+      <c r="H32" s="48">
+        <f>(E32*D32*5*D7)/0.94</f>
         <v>297872.3404255319</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I32" s="44">
         <f t="shared" si="0"/>
         <v>595744.68085106381</v>
       </c>
     </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C32" s="18" t="s">
+    <row r="33" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C33" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="47">
+      <c r="D33" s="47">
         <v>1</v>
       </c>
-      <c r="E32" s="43">
+      <c r="E33" s="43">
         <v>5000</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F33" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="43">
-        <f>(E32*D32*3*2)/0.94</f>
+      <c r="G33" s="43">
+        <f>(E33*D33*3*2)/0.94</f>
         <v>31914.89361702128</v>
       </c>
-      <c r="H32" s="48">
-        <f>(E32*D32*3*2)/0.94</f>
+      <c r="H33" s="48">
+        <f>(E33*D33*3*2)/0.94</f>
         <v>31914.89361702128</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I33" s="44">
         <f t="shared" si="0"/>
         <v>63829.78723404256</v>
       </c>
     </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C33" s="49" t="s">
+    <row r="34" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C34" s="49" t="s">
         <v>29</v>
-      </c>
-      <c r="D33" s="47">
-        <v>2</v>
-      </c>
-      <c r="E33" s="43">
-        <v>12000</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G33" s="43">
-        <f>(E33*D33*4)/0.94</f>
-        <v>102127.6595744681</v>
-      </c>
-      <c r="H33" s="50">
-        <f>(E33*D33*3)/0.94</f>
-        <v>76595.744680851072</v>
-      </c>
-      <c r="I33" s="44"/>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C34" s="18" t="s">
-        <v>31</v>
       </c>
       <c r="D34" s="47">
         <v>2</v>
       </c>
       <c r="E34" s="43">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G34" s="43">
-        <f>(E34*D34*3*D5)/0.94</f>
-        <v>89361.702127659577</v>
-      </c>
-      <c r="H34" s="48">
-        <f>(E34*D34*3*D6)/0.94</f>
-        <v>89361.702127659577</v>
+        <f>(E34*D34*4)/0.94</f>
+        <v>102127.6595744681</v>
+      </c>
+      <c r="H34" s="50">
+        <f>(E34*D34*3)/0.94</f>
+        <v>76595.744680851072</v>
       </c>
       <c r="I34" s="44">
         <f t="shared" si="0"/>
@@ -1397,104 +1397,130 @@
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C35" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="47">
+        <v>2</v>
+      </c>
+      <c r="E35" s="43">
+        <v>2000</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="43">
+        <f>(E35*D35*3*D6)/0.94</f>
+        <v>89361.702127659577</v>
+      </c>
+      <c r="H35" s="48">
+        <f>(E35*D35*3*D7)/0.94</f>
+        <v>89361.702127659577</v>
+      </c>
+      <c r="I35" s="44">
+        <f t="shared" si="0"/>
+        <v>178723.40425531915</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C36" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="46">
-        <f>25000*D5</f>
-        <v>175000</v>
-      </c>
-      <c r="H35" s="46">
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="46">
         <f>25000*D6</f>
         <v>175000</v>
       </c>
-      <c r="I35" s="35">
+      <c r="H36" s="46">
+        <f>25000*D7</f>
+        <v>175000</v>
+      </c>
+      <c r="I36" s="35">
         <f t="shared" si="0"/>
         <v>350000</v>
       </c>
     </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C36" s="18" t="s">
+    <row r="37" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C37" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="43">
+      <c r="D37" s="18"/>
+      <c r="E37" s="43">
         <v>280000</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F37" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G36" s="46">
-        <f>E36*2</f>
+      <c r="G37" s="46">
+        <f>E37*2</f>
         <v>560000</v>
       </c>
-      <c r="H36" s="40">
-        <f>E36*2</f>
+      <c r="H37" s="40">
+        <f>E37*2</f>
         <v>560000</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I37" s="35">
         <f t="shared" si="0"/>
         <v>1120000</v>
       </c>
     </row>
-    <row r="37" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C37" s="18" t="s">
+    <row r="38" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C38" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="43">
+      <c r="D38" s="18"/>
+      <c r="E38" s="43">
         <v>90000</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F38" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G37" s="37">
-        <f>E37*5</f>
+      <c r="G38" s="37">
+        <f>E38*5</f>
         <v>450000</v>
       </c>
-      <c r="H37" s="37">
-        <f>E37*5</f>
+      <c r="H38" s="37">
+        <f>E38*5</f>
         <v>450000</v>
       </c>
-      <c r="I37" s="35">
-        <f>G37+H37</f>
+      <c r="I38" s="35">
+        <f>G38+H38</f>
         <v>900000</v>
       </c>
     </row>
-    <row r="38" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C38" s="49" t="s">
+    <row r="39" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C39" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="51">
+      <c r="D39" s="49"/>
+      <c r="E39" s="51">
         <v>20000</v>
       </c>
-      <c r="F38" s="49" t="s">
+      <c r="F39" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="G38" s="52">
-        <f>E38*D5</f>
+      <c r="G39" s="52">
+        <f>E39*D6</f>
         <v>140000</v>
       </c>
-      <c r="H38" s="53">
-        <f>E38*D6</f>
+      <c r="H39" s="53">
+        <f>E39*D7</f>
         <v>140000</v>
       </c>
-      <c r="I38" s="35">
+      <c r="I39" s="35">
         <f t="shared" si="0"/>
         <v>280000</v>
       </c>
     </row>
-    <row r="39" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="54"/>
+    <row r="40" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
